--- a/backend/data/financials_by_company/0552.HK.xlsx
+++ b/backend/data/financials_by_company/0552.HK.xlsx
@@ -4364,10 +4364,8 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100073</t>
-        </is>
+      <c r="D2" t="n">
+        <v>100073</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4617,7 +4615,7 @@
         <v>1767139200</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>3610019072</v>
@@ -4720,7 +4718,7 @@
         <v>937715968</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
         <v>-0.032</v>
